--- a/Files/2-nd course/4-th semester/Probability theory/Laboratory work/Lab #2/Vlad/Теорвер.xlsx
+++ b/Files/2-nd course/4-th semester/Probability theory/Laboratory work/Lab #2/Vlad/Теорвер.xlsx
@@ -5,16 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Владислав\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Codespace\Files\2-nd course\4-th semester\Probability theory\Laboratory work\Lab #2\Vlad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C26C4B79-67F3-406E-8BD8-6B8FBF32BF4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09336A8-CA1A-4F52-8291-6B09CDBACB29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="348" windowWidth="30936" windowHeight="17040" xr2:uid="{238F68E3-D8EC-4A8A-AD0E-854BE4B44AFF}"/>
+    <workbookView xWindow="38280" yWindow="5640" windowWidth="25425" windowHeight="16440" activeTab="3" xr2:uid="{238F68E3-D8EC-4A8A-AD0E-854BE4B44AFF}"/>
   </bookViews>
   <sheets>
     <sheet name="Выборки" sheetId="1" r:id="rId1"/>
     <sheet name="Лист1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
+    <sheet name="Лист2" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,8 +36,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="45">
   <si>
     <t>X</t>
   </si>
@@ -75,6 +99,102 @@
   <si>
     <t>коэф вари</t>
   </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>W/h</t>
+  </si>
+  <si>
+    <t>Середина</t>
+  </si>
+  <si>
+    <t>[5,5; 6,38]</t>
+  </si>
+  <si>
+    <t>(6,38; 7,26]</t>
+  </si>
+  <si>
+    <t>(7,26; 8,14]</t>
+  </si>
+  <si>
+    <t>(8,14; 9,02]</t>
+  </si>
+  <si>
+    <t>(9,02; 9,9]</t>
+  </si>
+  <si>
+    <t>[16; 29,2]</t>
+  </si>
+  <si>
+    <t>(29,2; 42,4]</t>
+  </si>
+  <si>
+    <t>(42,4; 55,6]</t>
+  </si>
+  <si>
+    <t>(55,6; 68,8]</t>
+  </si>
+  <si>
+    <t>(68,8; 82]</t>
+  </si>
+  <si>
+    <t>[5,1857; 5,8227]</t>
+  </si>
+  <si>
+    <t>(5,8227; 6,4597]</t>
+  </si>
+  <si>
+    <t>(6,4597; 7,0967]</t>
+  </si>
+  <si>
+    <t>(7,0967; 7,7337]</t>
+  </si>
+  <si>
+    <t>(7,7337; 8,3707]</t>
+  </si>
+  <si>
+    <t>(8,3707; 9,0077]</t>
+  </si>
+  <si>
+    <t>(9,0077; 9,6447]</t>
+  </si>
+  <si>
+    <t>(9,6447; 10,2817</t>
+  </si>
+  <si>
+    <t>[11,2857; 20,8457]</t>
+  </si>
+  <si>
+    <t>(20,8457; 30,4057]</t>
+  </si>
+  <si>
+    <t>(30,4057; 39,9657]</t>
+  </si>
+  <si>
+    <t>(39,9657; 49,5257]</t>
+  </si>
+  <si>
+    <t>(49,5257; 59,0857]</t>
+  </si>
+  <si>
+    <t>(59,0857; 68,6457]</t>
+  </si>
+  <si>
+    <t>(68,6457; 78,2057]</t>
+  </si>
+  <si>
+    <t>(78,2057; 87,7657]</t>
+  </si>
+  <si>
+    <t>выбор ср</t>
+  </si>
+  <si>
+    <t>выб дисп</t>
+  </si>
 </sst>
 </file>
 
@@ -84,7 +204,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -138,8 +258,37 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -164,8 +313,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9CC2E5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -188,12 +343,77 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -240,6 +460,40 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -13942,6 +14196,1581 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист2!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>W/h</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист2!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>[5,5; 6,38]</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>(6,38; 7,26]</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>(7,26; 8,14]</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>(8,14; 9,02]</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>(9,02; 9,9]</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист2!$D$2:$D$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.22727273000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.13257575999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.20833333000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.30303029999999997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.26515151999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E3FB-4A75-A1D0-ECC873557892}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="772212136"/>
+        <c:axId val="772212496"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="772212136"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ru-RU"/>
+                  <a:t>Интервалы</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ru-RU"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="772212496"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="772212496"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>W/h</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ru-RU"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="772212136"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист2!$J$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>W/h</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист2!$G$2:$G$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>[16; 29,2]</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>(29,2; 42,4]</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>(42,4; 55,6]</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>(55,6; 68,8]</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>(68,8; 82]</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист2!$J$2:$J$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.24621199999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.359848</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.397727</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.113636</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.8939000000000001E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E2B8-4D5C-91B4-3074D72514AD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="758662192"/>
+        <c:axId val="758661832"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="758662192"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ru-RU"/>
+                  <a:t>Интервалы</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ru-RU"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="758661832"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="758661832"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>W/h</a:t>
+                </a:r>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ru-RU"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="758662192"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист2!$P$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>W/h</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист2!$M$2:$M$9</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>[5,1857; 5,8227]</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>(5,8227; 6,4597]</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>(6,4597; 7,0967]</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>(7,0967; 7,7337]</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>(7,7337; 8,3707]</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>(8,3707; 9,0077]</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>(9,0077; 9,6447]</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>(9,6447; 10,2817</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист2!$P$2:$P$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.15698599999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.15698599999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.8492999999999993E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.23547899999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.31397199999999997</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.26164300000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.26164300000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.104657</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D0AE-4873-B830-A5E59A78E2A3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="772484832"/>
+        <c:axId val="772485552"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="772484832"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ru-RU" sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Интервалы</a:t>
+                </a:r>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ru-RU"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="772485552"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="772485552"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>W/h</a:t>
+                </a:r>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ru-RU"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="772484832"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист2!$V$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>W/h</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист2!$S$2:$S$9</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>[11,2857; 20,8457]</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>(20,8457; 30,4057]</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>(30,4057; 39,9657]</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>(39,9657; 49,5257]</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>(49,5257; 59,0857]</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>(59,0857; 68,6457]</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>(68,6457; 78,2057]</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>(78,2057; 87,7657]</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист2!$V$2:$V$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>8.7170000000000008E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.7434000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.5689999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.4407000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.6151000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.0460000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.743E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A788-48AA-98CD-7942FEF81077}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="769783040"/>
+        <c:axId val="769780880"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="769783040"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ru-RU" sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Интервалы</a:t>
+                </a:r>
+                <a:endParaRPr lang="ru-RU" b="0"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ru-RU"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="769780880"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="769780880"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>W/h</a:t>
+                </a:r>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ru-RU"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="769783040"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -13983,6 +15812,166 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -15028,6 +17017,2018 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -15099,6 +19100,155 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>227647</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>465772</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>529590</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>154305</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Диаграмма 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F8D2506-9585-E38F-093E-05F3B8680EBC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>515302</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>79057</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>216217</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>107632</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Диаграмма 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F28FEBF0-77B8-8021-8957-7B0FFB2775A1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>439102</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>67627</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>391477</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>84772</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Диаграмма 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCDC03B9-6F1A-D58E-8AF5-9BC35DBEB2C1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>583882</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>37147</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>303847</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>58102</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Диаграмма 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9EC75E8-D3FF-8436-D09A-510F5FD5A7A3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -17452,4 +21602,1166 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3207102A-B4C1-4C48-96F6-E0F5D84CAB52}">
+  <dimension ref="A1:O22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16" style="24" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" style="24" customWidth="1"/>
+    <col min="3" max="4" width="15.109375" style="24" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.109375" style="24" customWidth="1"/>
+    <col min="6" max="7" width="8.88671875" style="24"/>
+    <col min="8" max="8" width="16" style="24" customWidth="1"/>
+    <col min="9" max="9" width="21.33203125" style="24" customWidth="1"/>
+    <col min="10" max="11" width="15.109375" style="24" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.109375" style="24" customWidth="1"/>
+    <col min="13" max="16384" width="8.88671875" style="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="25">
+        <v>16</v>
+      </c>
+      <c r="B2" s="25">
+        <f>A2+$O$3</f>
+        <v>29.2</v>
+      </c>
+      <c r="C2" s="29">
+        <v>13</v>
+      </c>
+      <c r="D2" s="23">
+        <f>C2/$N$2</f>
+        <v>0.21666666666666667</v>
+      </c>
+      <c r="E2" s="23">
+        <f>D2/$N$3</f>
+        <v>0.24621212121212122</v>
+      </c>
+      <c r="F2" s="25">
+        <f>(A2+B2)/2</f>
+        <v>22.6</v>
+      </c>
+      <c r="N2" s="24">
+        <f>SUM(C2:C6)</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="22">
+        <f>B2</f>
+        <v>29.2</v>
+      </c>
+      <c r="B3" s="25">
+        <f t="shared" ref="B3:B6" si="0">A3+$O$3</f>
+        <v>42.4</v>
+      </c>
+      <c r="C3" s="30">
+        <v>19</v>
+      </c>
+      <c r="D3" s="23">
+        <f>C3/$N$2</f>
+        <v>0.31666666666666665</v>
+      </c>
+      <c r="E3" s="23">
+        <f>D3/$N$3</f>
+        <v>0.35984848484848481</v>
+      </c>
+      <c r="F3" s="25">
+        <f t="shared" ref="F3:F6" si="1">(A3+B3)/2</f>
+        <v>35.799999999999997</v>
+      </c>
+      <c r="N3" s="24">
+        <v>0.88</v>
+      </c>
+      <c r="O3" s="24">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="22">
+        <f t="shared" ref="A4:A6" si="2">B3</f>
+        <v>42.4</v>
+      </c>
+      <c r="B4" s="25">
+        <f t="shared" si="0"/>
+        <v>55.599999999999994</v>
+      </c>
+      <c r="C4" s="30">
+        <v>21</v>
+      </c>
+      <c r="D4" s="23">
+        <f>C4/$N$2</f>
+        <v>0.35</v>
+      </c>
+      <c r="E4" s="23">
+        <f>D4/$N$3</f>
+        <v>0.39772727272727271</v>
+      </c>
+      <c r="F4" s="25">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="22">
+        <f t="shared" si="2"/>
+        <v>55.599999999999994</v>
+      </c>
+      <c r="B5" s="25">
+        <f t="shared" si="0"/>
+        <v>68.8</v>
+      </c>
+      <c r="C5" s="30">
+        <v>6</v>
+      </c>
+      <c r="D5" s="23">
+        <f>C5/$N$2</f>
+        <v>0.1</v>
+      </c>
+      <c r="E5" s="23">
+        <f>D5/$N$3</f>
+        <v>0.11363636363636365</v>
+      </c>
+      <c r="F5" s="25">
+        <f t="shared" si="1"/>
+        <v>62.199999999999996</v>
+      </c>
+      <c r="N5" s="28">
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="O5" s="28">
+        <v>9.56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="22">
+        <f t="shared" si="2"/>
+        <v>68.8</v>
+      </c>
+      <c r="B6" s="25">
+        <f t="shared" si="0"/>
+        <v>82</v>
+      </c>
+      <c r="C6" s="30">
+        <v>1</v>
+      </c>
+      <c r="D6" s="23">
+        <f>C6/$N$2</f>
+        <v>1.6666666666666666E-2</v>
+      </c>
+      <c r="E6" s="23">
+        <f>D6/$N$3</f>
+        <v>1.893939393939394E-2</v>
+      </c>
+      <c r="F6" s="25">
+        <f t="shared" si="1"/>
+        <v>75.400000000000006</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C7" s="24">
+        <f>SUM(C2:C6)</f>
+        <v>60</v>
+      </c>
+      <c r="D7" s="24">
+        <f t="shared" ref="D7:E7" si="3">SUM(D2:D6)</f>
+        <v>1</v>
+      </c>
+      <c r="E7" s="24">
+        <f t="shared" si="3"/>
+        <v>1.1363636363636362</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="14" spans="1:15" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="27"/>
+      <c r="C14" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="I14" s="27"/>
+      <c r="J14" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="K14" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="L14" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="M14" s="21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="25">
+        <v>5.1856999999999998</v>
+      </c>
+      <c r="B15" s="25">
+        <f>A15+$N$5</f>
+        <v>5.8226999999999993</v>
+      </c>
+      <c r="C15" s="25">
+        <v>6</v>
+      </c>
+      <c r="D15" s="23">
+        <f>C15/$N$2</f>
+        <v>0.1</v>
+      </c>
+      <c r="E15" s="23">
+        <f>D15/$N$5</f>
+        <v>0.15698587127158556</v>
+      </c>
+      <c r="F15" s="25">
+        <f>(A15+B15)/2</f>
+        <v>5.5041999999999991</v>
+      </c>
+      <c r="H15" s="25">
+        <v>11.2857</v>
+      </c>
+      <c r="I15" s="25">
+        <f>H15+$O$5</f>
+        <v>20.845700000000001</v>
+      </c>
+      <c r="J15" s="25">
+        <v>5</v>
+      </c>
+      <c r="K15" s="23">
+        <f>J15/$N$2</f>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="L15" s="23">
+        <f>K15/$O$5</f>
+        <v>8.7168758716875856E-3</v>
+      </c>
+      <c r="M15" s="25">
+        <f>(H15+I15)/2</f>
+        <v>16.0657</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="22">
+        <f>B15</f>
+        <v>5.8226999999999993</v>
+      </c>
+      <c r="B16" s="25">
+        <f t="shared" ref="B16:B22" si="4">A16+$N$5</f>
+        <v>6.4596999999999998</v>
+      </c>
+      <c r="C16" s="22">
+        <v>6</v>
+      </c>
+      <c r="D16" s="23">
+        <f>C16/$N$2</f>
+        <v>0.1</v>
+      </c>
+      <c r="E16" s="23">
+        <f t="shared" ref="E16:E22" si="5">D16/$N$5</f>
+        <v>0.15698587127158556</v>
+      </c>
+      <c r="F16" s="25">
+        <f t="shared" ref="F16:F22" si="6">(A16+B16)/2</f>
+        <v>6.1411999999999995</v>
+      </c>
+      <c r="H16" s="22">
+        <f>I15</f>
+        <v>20.845700000000001</v>
+      </c>
+      <c r="I16" s="25">
+        <f t="shared" ref="I16:I22" si="7">H16+$O$5</f>
+        <v>30.405700000000003</v>
+      </c>
+      <c r="J16" s="22">
+        <v>10</v>
+      </c>
+      <c r="K16" s="23">
+        <f>J16/$N$2</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="L16" s="23">
+        <f t="shared" ref="L16:L22" si="8">K16/$O$5</f>
+        <v>1.7433751743375171E-2</v>
+      </c>
+      <c r="M16" s="25">
+        <f t="shared" ref="M16:M22" si="9">(H16+I16)/2</f>
+        <v>25.625700000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="22">
+        <f t="shared" ref="A17:A22" si="10">B16</f>
+        <v>6.4596999999999998</v>
+      </c>
+      <c r="B17" s="25">
+        <f t="shared" si="4"/>
+        <v>7.0967000000000002</v>
+      </c>
+      <c r="C17" s="22">
+        <v>3</v>
+      </c>
+      <c r="D17" s="23">
+        <f>C17/$N$2</f>
+        <v>0.05</v>
+      </c>
+      <c r="E17" s="23">
+        <f t="shared" si="5"/>
+        <v>7.8492935635792779E-2</v>
+      </c>
+      <c r="F17" s="25">
+        <f t="shared" si="6"/>
+        <v>6.7782</v>
+      </c>
+      <c r="H17" s="22">
+        <f t="shared" ref="H17:H22" si="11">I16</f>
+        <v>30.405700000000003</v>
+      </c>
+      <c r="I17" s="25">
+        <f t="shared" si="7"/>
+        <v>39.965700000000005</v>
+      </c>
+      <c r="J17" s="22">
+        <v>9</v>
+      </c>
+      <c r="K17" s="23">
+        <f>J17/$N$2</f>
+        <v>0.15</v>
+      </c>
+      <c r="L17" s="23">
+        <f t="shared" si="8"/>
+        <v>1.5690376569037656E-2</v>
+      </c>
+      <c r="M17" s="25">
+        <f t="shared" si="9"/>
+        <v>35.185700000000004</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="22">
+        <f t="shared" si="10"/>
+        <v>7.0967000000000002</v>
+      </c>
+      <c r="B18" s="25">
+        <f t="shared" si="4"/>
+        <v>7.7337000000000007</v>
+      </c>
+      <c r="C18" s="22">
+        <v>9</v>
+      </c>
+      <c r="D18" s="23">
+        <f>C18/$N$2</f>
+        <v>0.15</v>
+      </c>
+      <c r="E18" s="23">
+        <f t="shared" si="5"/>
+        <v>0.23547880690737832</v>
+      </c>
+      <c r="F18" s="25">
+        <f t="shared" si="6"/>
+        <v>7.4152000000000005</v>
+      </c>
+      <c r="H18" s="22">
+        <f t="shared" si="11"/>
+        <v>39.965700000000005</v>
+      </c>
+      <c r="I18" s="25">
+        <f t="shared" si="7"/>
+        <v>49.525700000000008</v>
+      </c>
+      <c r="J18" s="22">
+        <v>14</v>
+      </c>
+      <c r="K18" s="23">
+        <f>J18/$N$2</f>
+        <v>0.23333333333333334</v>
+      </c>
+      <c r="L18" s="23">
+        <f t="shared" si="8"/>
+        <v>2.4407252440725242E-2</v>
+      </c>
+      <c r="M18" s="25">
+        <f t="shared" si="9"/>
+        <v>44.745700000000006</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="22">
+        <f t="shared" si="10"/>
+        <v>7.7337000000000007</v>
+      </c>
+      <c r="B19" s="25">
+        <f t="shared" si="4"/>
+        <v>8.3707000000000011</v>
+      </c>
+      <c r="C19" s="22">
+        <v>12</v>
+      </c>
+      <c r="D19" s="23">
+        <f>C19/$N$2</f>
+        <v>0.2</v>
+      </c>
+      <c r="E19" s="23">
+        <f t="shared" si="5"/>
+        <v>0.31397174254317112</v>
+      </c>
+      <c r="F19" s="25">
+        <f t="shared" si="6"/>
+        <v>8.0522000000000009</v>
+      </c>
+      <c r="H19" s="22">
+        <f t="shared" si="11"/>
+        <v>49.525700000000008</v>
+      </c>
+      <c r="I19" s="25">
+        <f t="shared" si="7"/>
+        <v>59.08570000000001</v>
+      </c>
+      <c r="J19" s="22">
+        <v>15</v>
+      </c>
+      <c r="K19" s="23">
+        <f>J19/$N$2</f>
+        <v>0.25</v>
+      </c>
+      <c r="L19" s="23">
+        <f t="shared" si="8"/>
+        <v>2.615062761506276E-2</v>
+      </c>
+      <c r="M19" s="25">
+        <f t="shared" si="9"/>
+        <v>54.305700000000009</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="22">
+        <f t="shared" si="10"/>
+        <v>8.3707000000000011</v>
+      </c>
+      <c r="B20" s="25">
+        <f t="shared" si="4"/>
+        <v>9.0077000000000016</v>
+      </c>
+      <c r="C20" s="22">
+        <v>10</v>
+      </c>
+      <c r="D20" s="23">
+        <f t="shared" ref="D20:D22" si="12">C20/$N$2</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="E20" s="23">
+        <f t="shared" si="5"/>
+        <v>0.2616431187859759</v>
+      </c>
+      <c r="F20" s="25">
+        <f t="shared" si="6"/>
+        <v>8.6892000000000014</v>
+      </c>
+      <c r="H20" s="22">
+        <f t="shared" si="11"/>
+        <v>59.08570000000001</v>
+      </c>
+      <c r="I20" s="25">
+        <f t="shared" si="7"/>
+        <v>68.645700000000005</v>
+      </c>
+      <c r="J20" s="22">
+        <v>6</v>
+      </c>
+      <c r="K20" s="23">
+        <f t="shared" ref="K20:K22" si="13">J20/$N$2</f>
+        <v>0.1</v>
+      </c>
+      <c r="L20" s="23">
+        <f t="shared" si="8"/>
+        <v>1.0460251046025104E-2</v>
+      </c>
+      <c r="M20" s="25">
+        <f t="shared" si="9"/>
+        <v>63.865700000000004</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="22">
+        <f t="shared" si="10"/>
+        <v>9.0077000000000016</v>
+      </c>
+      <c r="B21" s="25">
+        <f t="shared" si="4"/>
+        <v>9.644700000000002</v>
+      </c>
+      <c r="C21" s="22">
+        <v>10</v>
+      </c>
+      <c r="D21" s="23">
+        <f t="shared" si="12"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="E21" s="23">
+        <f t="shared" si="5"/>
+        <v>0.2616431187859759</v>
+      </c>
+      <c r="F21" s="25">
+        <f t="shared" si="6"/>
+        <v>9.3262000000000018</v>
+      </c>
+      <c r="H21" s="22">
+        <f t="shared" si="11"/>
+        <v>68.645700000000005</v>
+      </c>
+      <c r="I21" s="25">
+        <f t="shared" si="7"/>
+        <v>78.205700000000007</v>
+      </c>
+      <c r="J21" s="22">
+        <v>0</v>
+      </c>
+      <c r="K21" s="23">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="23">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M21" s="25">
+        <f t="shared" si="9"/>
+        <v>73.425700000000006</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="22">
+        <f t="shared" si="10"/>
+        <v>9.644700000000002</v>
+      </c>
+      <c r="B22" s="25">
+        <f t="shared" si="4"/>
+        <v>10.281700000000003</v>
+      </c>
+      <c r="C22" s="22">
+        <v>4</v>
+      </c>
+      <c r="D22" s="23">
+        <f t="shared" si="12"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="E22" s="23">
+        <f t="shared" si="5"/>
+        <v>0.10465724751439037</v>
+      </c>
+      <c r="F22" s="25">
+        <f t="shared" si="6"/>
+        <v>9.9632000000000023</v>
+      </c>
+      <c r="H22" s="22">
+        <f t="shared" si="11"/>
+        <v>78.205700000000007</v>
+      </c>
+      <c r="I22" s="25">
+        <f t="shared" si="7"/>
+        <v>87.76570000000001</v>
+      </c>
+      <c r="J22" s="22">
+        <v>1</v>
+      </c>
+      <c r="K22" s="23">
+        <f t="shared" si="13"/>
+        <v>1.6666666666666666E-2</v>
+      </c>
+      <c r="L22" s="23">
+        <f t="shared" si="8"/>
+        <v>1.7433751743375172E-3</v>
+      </c>
+      <c r="M22" s="25">
+        <f t="shared" si="9"/>
+        <v>82.985700000000008</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="H14:I14"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10126FE8-435A-4CB6-85E1-E1659673A08F}">
+  <dimension ref="A1:Z9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="13" max="13" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.77734375" customWidth="1"/>
+    <col min="20" max="20" width="4" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="T1" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="U1" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="V1" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="W1" s="21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="23">
+        <v>12</v>
+      </c>
+      <c r="C2" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="D2" s="31">
+        <v>0.22727273000000001</v>
+      </c>
+      <c r="E2" s="23">
+        <v>5.94</v>
+      </c>
+      <c r="F2">
+        <f>SUMPRODUCT(E2:E6,C2:C6)</f>
+        <v>7.9173333277999998</v>
+      </c>
+      <c r="G2" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="31">
+        <v>13</v>
+      </c>
+      <c r="I2" s="31">
+        <v>0.21666667000000001</v>
+      </c>
+      <c r="J2" s="31">
+        <v>0.24621199999999999</v>
+      </c>
+      <c r="K2" s="31">
+        <v>22.6</v>
+      </c>
+      <c r="L2">
+        <f>SUMPRODUCT(K2:K6,I2:I6)</f>
+        <v>40.860000445999994</v>
+      </c>
+      <c r="M2" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="23">
+        <v>6</v>
+      </c>
+      <c r="O2" s="31">
+        <v>0.1</v>
+      </c>
+      <c r="P2" s="31">
+        <v>0.15698599999999999</v>
+      </c>
+      <c r="Q2" s="31">
+        <v>5.5042</v>
+      </c>
+      <c r="R2">
+        <f>SUMPRODUCT(Q2:Q9,O2:O9)</f>
+        <v>7.8929500932619989</v>
+      </c>
+      <c r="S2" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="T2" s="31">
+        <v>5</v>
+      </c>
+      <c r="U2" s="31">
+        <v>8.3333329999999997E-2</v>
+      </c>
+      <c r="V2" s="31">
+        <v>8.7170000000000008E-3</v>
+      </c>
+      <c r="W2" s="31">
+        <v>16.065999999999999</v>
+      </c>
+      <c r="X2">
+        <f>SUMPRODUCT(W2:W9,U2:U9)</f>
+        <v>42.674666825999999</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="23">
+        <v>7</v>
+      </c>
+      <c r="C3" s="31">
+        <v>0.11666667</v>
+      </c>
+      <c r="D3" s="31">
+        <v>0.13257575999999999</v>
+      </c>
+      <c r="E3" s="23">
+        <v>6.82</v>
+      </c>
+      <c r="F3" cm="1">
+        <f t="array" ref="F3">SUMPRODUCT((E2:E6-F2)^2,C2:C6)</f>
+        <v>1.6415128867513777</v>
+      </c>
+      <c r="G3" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="31">
+        <v>19</v>
+      </c>
+      <c r="I3" s="31">
+        <v>0.31666666999999998</v>
+      </c>
+      <c r="J3" s="31">
+        <v>0.359848</v>
+      </c>
+      <c r="K3" s="31">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="L3" cm="1">
+        <f t="array" ref="L3">SUMPRODUCT((K2:K6-L2)^2,I2:I6)</f>
+        <v>168.96440517347619</v>
+      </c>
+      <c r="M3" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="N3" s="23">
+        <v>6</v>
+      </c>
+      <c r="O3" s="31">
+        <v>0.1</v>
+      </c>
+      <c r="P3" s="31">
+        <v>0.15698599999999999</v>
+      </c>
+      <c r="Q3" s="31">
+        <v>6.1412000000000004</v>
+      </c>
+      <c r="R3" cm="1">
+        <f t="array" ref="R3">SUMPRODUCT((Q2:Q9-R2)^2,O2:O9)</f>
+        <v>1.7126833440805216</v>
+      </c>
+      <c r="S3" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="T3" s="31">
+        <v>10</v>
+      </c>
+      <c r="U3" s="31">
+        <v>0.16666666999999999</v>
+      </c>
+      <c r="V3" s="31">
+        <v>1.7434000000000002E-2</v>
+      </c>
+      <c r="W3" s="31">
+        <v>25.626000000000001</v>
+      </c>
+      <c r="X3" cm="1">
+        <f t="array" ref="X3">SUMPRODUCT((W2:W9-X2)^2,U2:U9)</f>
+        <v>222.67035556671908</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="23">
+        <v>11</v>
+      </c>
+      <c r="C4" s="31">
+        <v>0.18333332999999999</v>
+      </c>
+      <c r="D4" s="31">
+        <v>0.20833333000000001</v>
+      </c>
+      <c r="E4" s="23">
+        <v>7.7</v>
+      </c>
+      <c r="F4">
+        <f>SQRT(F3)</f>
+        <v>1.2812153943624693</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="31">
+        <v>21</v>
+      </c>
+      <c r="I4" s="31">
+        <v>0.35</v>
+      </c>
+      <c r="J4" s="31">
+        <v>0.397727</v>
+      </c>
+      <c r="K4" s="31">
+        <v>49</v>
+      </c>
+      <c r="L4">
+        <f>SQRT(L3)</f>
+        <v>12.998630896116568</v>
+      </c>
+      <c r="M4" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" s="23">
+        <v>3</v>
+      </c>
+      <c r="O4" s="31">
+        <v>0.05</v>
+      </c>
+      <c r="P4" s="31">
+        <v>7.8492999999999993E-2</v>
+      </c>
+      <c r="Q4" s="31">
+        <v>6.7782</v>
+      </c>
+      <c r="R4">
+        <f>SQRT(R3)</f>
+        <v>1.3086952831276353</v>
+      </c>
+      <c r="S4" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="T4" s="31">
+        <v>9</v>
+      </c>
+      <c r="U4" s="31">
+        <v>0.15</v>
+      </c>
+      <c r="V4" s="31">
+        <v>1.5689999999999999E-2</v>
+      </c>
+      <c r="W4" s="31">
+        <v>35.186</v>
+      </c>
+      <c r="X4">
+        <f>SQRT(X3)</f>
+        <v>14.922143129145997</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="23">
+        <v>16</v>
+      </c>
+      <c r="C5" s="31">
+        <v>0.26666666999999999</v>
+      </c>
+      <c r="D5" s="31">
+        <v>0.30303029999999997</v>
+      </c>
+      <c r="E5" s="23">
+        <v>8.68</v>
+      </c>
+      <c r="G5" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="31">
+        <v>6</v>
+      </c>
+      <c r="I5" s="31">
+        <v>0.1</v>
+      </c>
+      <c r="J5" s="31">
+        <v>0.113636</v>
+      </c>
+      <c r="K5" s="31">
+        <v>62.2</v>
+      </c>
+      <c r="M5" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="N5" s="23">
+        <v>9</v>
+      </c>
+      <c r="O5" s="31">
+        <v>0.15</v>
+      </c>
+      <c r="P5" s="31">
+        <v>0.23547899999999999</v>
+      </c>
+      <c r="Q5" s="31">
+        <v>7.4151999999999996</v>
+      </c>
+      <c r="S5" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="T5" s="31">
+        <v>14</v>
+      </c>
+      <c r="U5" s="31">
+        <v>0.23333333000000001</v>
+      </c>
+      <c r="V5" s="31">
+        <v>2.4407000000000002E-2</v>
+      </c>
+      <c r="W5" s="31">
+        <v>44.746000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="23">
+        <v>14</v>
+      </c>
+      <c r="C6" s="31">
+        <v>0.23333333000000001</v>
+      </c>
+      <c r="D6" s="31">
+        <v>0.26515151999999997</v>
+      </c>
+      <c r="E6" s="23">
+        <v>9.4600000000000009</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="31">
+        <v>1</v>
+      </c>
+      <c r="I6" s="31">
+        <v>1.6666670000000001E-2</v>
+      </c>
+      <c r="J6" s="31">
+        <v>1.8939000000000001E-2</v>
+      </c>
+      <c r="K6" s="31">
+        <v>75.400000000000006</v>
+      </c>
+      <c r="M6" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="N6" s="23">
+        <v>12</v>
+      </c>
+      <c r="O6" s="31">
+        <v>0.2</v>
+      </c>
+      <c r="P6" s="31">
+        <v>0.31397199999999997</v>
+      </c>
+      <c r="Q6" s="31">
+        <v>8.0521999999999991</v>
+      </c>
+      <c r="S6" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="T6" s="31">
+        <v>15</v>
+      </c>
+      <c r="U6" s="31">
+        <v>0.25</v>
+      </c>
+      <c r="V6" s="31">
+        <v>2.6151000000000001E-2</v>
+      </c>
+      <c r="W6" s="31">
+        <v>54.305999999999997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M7" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="N7" s="23">
+        <v>10</v>
+      </c>
+      <c r="O7" s="31">
+        <v>0.16666666999999999</v>
+      </c>
+      <c r="P7" s="31">
+        <v>0.26164300000000001</v>
+      </c>
+      <c r="Q7" s="31">
+        <v>8.6891999999999996</v>
+      </c>
+      <c r="S7" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="T7" s="31">
+        <v>6</v>
+      </c>
+      <c r="U7" s="31">
+        <v>0.1</v>
+      </c>
+      <c r="V7" s="31">
+        <v>1.0460000000000001E-2</v>
+      </c>
+      <c r="W7" s="31">
+        <v>63.866</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M8" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="N8" s="23">
+        <v>10</v>
+      </c>
+      <c r="O8" s="31">
+        <v>0.16666666999999999</v>
+      </c>
+      <c r="P8" s="31">
+        <v>0.26164300000000001</v>
+      </c>
+      <c r="Q8" s="31">
+        <v>9.3262</v>
+      </c>
+      <c r="S8" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="T8" s="31">
+        <v>0</v>
+      </c>
+      <c r="U8" s="31">
+        <v>0</v>
+      </c>
+      <c r="V8" s="31">
+        <v>0</v>
+      </c>
+      <c r="W8" s="31">
+        <v>73.426000000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="N9" s="23">
+        <v>4</v>
+      </c>
+      <c r="O9" s="31">
+        <v>6.6666669999999997E-2</v>
+      </c>
+      <c r="P9" s="31">
+        <v>0.104657</v>
+      </c>
+      <c r="Q9" s="31">
+        <v>9.9632000000000005</v>
+      </c>
+      <c r="S9" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="T9" s="31">
+        <v>1</v>
+      </c>
+      <c r="U9" s="31">
+        <v>1.6666670000000001E-2</v>
+      </c>
+      <c r="V9" s="31">
+        <v>1.743E-3</v>
+      </c>
+      <c r="W9" s="31">
+        <v>82.986000000000004</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>